--- a/artfynd/S 3895-2024 artfynd.xlsx
+++ b/artfynd/S 3895-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3032,6 +3032,550 @@
       <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129013160</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137259429</v>
+      </c>
+      <c r="B18" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bromsmuren, Gstr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>614250</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6723106</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>20 grader varmt, halvklart, 3-4 m/s, nord-östlig vind, 50% sol.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137259429</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137259496</v>
+      </c>
+      <c r="B19" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bromsmuren, Gstr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>614244</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6723108</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>20 grader varmt, halvklart, 3-4 m/s, nord-östlig vind, 50% sol.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137259496</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137259498</v>
+      </c>
+      <c r="B20" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bromsmuren, Gstr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>614246</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6723107</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>20 grader varmt, halvklart, 3-4 m/s, nord-östlig vind, 50% sol.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137259498</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137259499</v>
+      </c>
+      <c r="B21" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bromsmuren, Gstr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>614250</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6723108</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>20 grader varmt, halvklart, 3-4 m/s, nord-östlig vind, 50% sol.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137259499</t>
         </is>
       </c>
     </row>
@@ -3053,6 +3597,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3895-2024 artfynd.xlsx
+++ b/artfynd/S 3895-2024 artfynd.xlsx
@@ -3040,7 +3040,7 @@
         <v>137259429</v>
       </c>
       <c r="B18" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>137259496</v>
       </c>
       <c r="B19" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>137259498</v>
       </c>
       <c r="B20" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137259499</v>
       </c>
       <c r="B21" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/S 3895-2024 artfynd.xlsx
+++ b/artfynd/S 3895-2024 artfynd.xlsx
@@ -3040,7 +3040,7 @@
         <v>137259429</v>
       </c>
       <c r="B18" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>137259496</v>
       </c>
       <c r="B19" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>137259498</v>
       </c>
       <c r="B20" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137259499</v>
       </c>
       <c r="B21" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
